--- a/PAMF_DIG F2 - monthly2026-07-24.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-24.xlsx
@@ -6838,7 +6838,7 @@
         <v>0.09</v>
       </c>
       <c r="N88" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>0.09</v>
       </c>
       <c r="N157" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>0.09</v>
       </c>
       <c r="N204" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>0.09</v>
       </c>
       <c r="N211" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>0.09</v>
       </c>
       <c r="N243" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O243" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>0.09</v>
       </c>
       <c r="N283" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O283" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>0.09</v>
       </c>
       <c r="N284" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O284" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>0.09</v>
       </c>
       <c r="N299" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>0.09</v>
       </c>
       <c r="N363" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O363" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-24.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-24.xlsx
@@ -925,7 +925,7 @@
         <v>0.09</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>0.09</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>0.09</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>0.09</v>
       </c>
       <c r="N38" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>0.09</v>
       </c>
       <c r="N66" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>0.09</v>
       </c>
       <c r="N67" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>0.09</v>
       </c>
       <c r="N71" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>0.09</v>
       </c>
       <c r="N77" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>0.09</v>
       </c>
       <c r="N87" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>0.09</v>
       </c>
       <c r="N92" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>0.09</v>
       </c>
       <c r="N96" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>0.09</v>
       </c>
       <c r="N105" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>0.09</v>
       </c>
       <c r="N110" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>0.09</v>
       </c>
       <c r="N111" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>0.09</v>
       </c>
       <c r="N140" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>0.09</v>
       </c>
       <c r="N144" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>0.09</v>
       </c>
       <c r="N145" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>0.09</v>
       </c>
       <c r="N152" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>0.09</v>
       </c>
       <c r="N167" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>0.09</v>
       </c>
       <c r="N172" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>0.09</v>
       </c>
       <c r="N176" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>0.09</v>
       </c>
       <c r="N178" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>0.09</v>
       </c>
       <c r="N185" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>0.09</v>
       </c>
       <c r="N189" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>0.09</v>
       </c>
       <c r="N198" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>0.09</v>
       </c>
       <c r="N228" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>0.09</v>
       </c>
       <c r="N246" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>0.09</v>
       </c>
       <c r="N250" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O250" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>0.09</v>
       </c>
       <c r="N252" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O252" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>0.09</v>
       </c>
       <c r="N277" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O277" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>0.09</v>
       </c>
       <c r="N280" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O280" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>0.09</v>
       </c>
       <c r="N319" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>0.09</v>
       </c>
       <c r="N322" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O322" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>0.09</v>
       </c>
       <c r="N340" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O340" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>0.09</v>
       </c>
       <c r="N347" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O347" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>0.09</v>
       </c>
       <c r="N352" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O352" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>0.09</v>
       </c>
       <c r="N355" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O355" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>0.09</v>
       </c>
       <c r="N361" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O361" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>0.09</v>
       </c>
       <c r="N370" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O370" t="inlineStr">
         <is>
